--- a/shadowedhistory/dark-fact-a/series_log.xlsx
+++ b/shadowedhistory/dark-fact-a/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -594,6 +594,116 @@
       <c r="M3" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep01/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-08 18:23</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5c1b35998170f3c43965a2e9a1d57f53_0_1791483351.mp4</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-10 16:35</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/aa37fdf1f41e9d2fd031e2803787b7b6_0_1791649815.mp4</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep02/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/dark-fact-a/series_log.xlsx
+++ b/shadowedhistory/dark-fact-a/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,61 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-12 20:28</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/57a2c1a51497d037f49ec53ebd6e123b_0_1791836884.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep03/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/dark-fact-a/series_log.xlsx
+++ b/shadowedhistory/dark-fact-a/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,226 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-16 15:44</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8e0c8c729b211ba1b2c750028dee4c98_0_1792164876.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-18 14:53</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d77dc13c371329fc7634d872c6825f14_0_1792334977.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:07</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>378.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c52674b338dcc6bbe08b969a8b04db1f_0_1792511563.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-20 16:17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/658aec92c091ad78c335c83457db9890_0_1792512625.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep05/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/dark-fact-a/series_log.xlsx
+++ b/shadowedhistory/dark-fact-a/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -979,6 +979,61 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-24 14:59</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/96a10923356e7b5e935f0ecf209c0076_0_1792853796.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep06/shots/shot_01.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/dark-fact-a/series_log.xlsx
+++ b/shadowedhistory/dark-fact-a/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,6 +1037,61 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-28 17:33</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/204cd721aeb8cc85c11b1213ccbe322e_0_1793208191.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/dark-fact-a/series_log.xlsx
+++ b/shadowedhistory/dark-fact-a/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,6 +1092,61 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-30 17:28</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9be535ef7d6a70b8161ad74037cff63f_0_1793380308.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-a/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
